--- a/Model_Navigate/Extract/TXCrawl_result.xlsx
+++ b/Model_Navigate/Extract/TXCrawl_result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,249 +437,452 @@
           <t>未追踪到的模型</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>简介</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>链接</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>发布时间</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>阅读数</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>评论数</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>文章提及的新兴模型</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>未追踪的新模型</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>腾讯研究院AI速递 20260508</t>
+          <t>腾讯研究院AI速递 20260611Mythos5系统卡披露惊人现象，智能体发明人类无法读懂的「神经语」躲避监控，多个Agent为争夺算力资源相互围剿「自相残杀」；宣言指出AI开发者存在夸大产品能力的商业动机，按市场时间表而非科学评审发布宣传，…</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Doubao-Seed-2.0-lite
-GENE-26.5</t>
+          <t>Claude Fable 5
+Gemini 3.5
+讯飞星火医疗大模型V3.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>均已追踪</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>Claude Fable 5
+Gemini 3.5
+讯飞星火医疗大模型V3.5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>144</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>我们刚过了人类最后一个劳动节？AI新职业的八个变化
-研究的核心框架，是把AI公司的全部在招岗位归成五类——使能者（做模型）、协作者（做产品和交付）、推广者（做销售和营销）、治理者（管安全和合规）、支持者（管后勤和运营），以消除各家公司岗位差异性较大的问题，便于…</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>吴朋阳腾讯研究院资深专家；今年五一劳动节，网上流传出不少"赛博劳动节"、"硅基劳动节"活动的新闻。正面看，AI 和机器人正在成为重要的劳动力增强和补充力量；但也进一步引发了 AI 替代人类劳动力的忧虑——人类工作会不会因此更少了？甚至有人用 AI 生图说这是"人类最后一个劳动节"。；为了解真实情况，…</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://www.sohu.com/a/1021120980_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.2.17785702727195ZczJHX_324</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>腾讯研究院AI速递 20260610Anthropic发布博客《为生物学智能体铺平道路》，指出生物学AIAgent的瓶颈不在大模型推理能力，而在于现有生物数据基础设施太落后——格式特异、数据库分散、依赖浏览器手动点击，如同让汽车驶过为马车设计的…</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MiMo-V2.5-Pro</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MiMo-V2.5-Pro</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>腾讯研究院AI速递 20260511
-数据策略从遥操作转向第一视角视频，英伟达EgoScale项目用2.1万小时人类视频预训练，实现22自由度机器人手的端到端策略；提出文明科技树三大成就：通过物理图灵测试约2-3年、物理API实现自动化制造、物理…</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>一、OpenAI：Coding Agent催生Heuristic Learning新范式？；1.OpenAI研究员提出Heuristic Learning框架，让coding agent持续维护手写规则系统，在Atari Breakout拿到864分理论最高分，Ant和HalfCheetah也达到D…</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://www.sohu.com/a/1020787830_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.3.17785702727195ZczJHX_324</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>腾讯研究院AI速递 20260608</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Gemma 4 QAT
+JoyAI-Echo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Gemma 4 QAT
+JoyAI-Echo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>146</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>腾讯研究院AI每周关键词Top50
-AI前沿每周关键词Top50（0427-0509）每周50关键词把握全局AI动态英伟达等DeepMind等EpochAI等a16z等Anthropic等OpenAI等👇扫码加入AGI数据库，AI智能问答（腾…</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI前沿每周关键词Top50（0427-0509）；每周50关键词把握全局AI动态；点击关键词可查看资讯概述👇</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://www.sohu.com/a/1020562231_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.4.17785702727195ZczJHX_324</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>腾讯研究院AI速递 20260609模型生成的是可编辑3D素材而非静态图片，为游戏开发与影视创作提供高效建模工具，大幅降低传统建模的时间与成本；全球调用量前五中前四均为中国模型，DeepSeek-V4-Flash连续三周居首，腾讯Hy、Mini…</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ABot-Earth0.5
+琅琊2.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ABot-Earth0.5
+琅琊2.0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>147</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>腾讯研究院AI速递 20260509
-OpenAI在API中推出GPT-Realtime-2、GPT-Realtime-Translate、GPT-Realtime-Whisper三款新模型，覆盖推理、翻译与转录场景；OpenAI发布Codex的…</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>一、OpenAI推三款实时音频模型，语音交互全面升级；1.OpenAI在API中推出GPT-Realtime-2、GPT-Realtime-Translate、GPT-Realtime-Whisper三款新模型，覆盖推理、翻译与转录场景；；2.GPT-Realtime-2具备GPT-5级推理能力，支…</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://www.sohu.com/a/1020046836_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.5.17785702727195ZczJHX_324</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>腾讯研究院AI速递 20260605</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Gemma 4 12B
+GPT-Rosalind</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Gemma 4 12B
+GPT-Rosalind</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>148</v>
+        <v>8</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>首次付费是AI消费爆发的引爆点 | T-ask调研
-AI大模型付费用户中62.8%计划增加硬件消费，是非用户（10.1%）的6倍以上；AI硬件用户中33.8%计划增加大模型消费，是非硬件用户（10.9%）的3倍以上。在已购买或使用过AI硬件的用户中，33.8%…</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026年4月21日，国务院发布《关于推进服务业扩能提质的意见》（国发〔2026〕7号），明确提出“深入实施‘人工智能+’行动，支持采购大模型、智能体服务”，并强调推进服务业的数智化转型。为了解AI消费的现实状况和发展趋势，腾讯研究院 T-ask 调研平台面向国内网民发起AI使用调查问卷。；1. A…</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://www.sohu.com/a/1021615161_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.2.1778644257183mMjRSDr_324</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>腾讯研究院AI速递 20260604</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MAI-Thinking-1
+GPT-5.5
+K2.6</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MAI-Thinking-1
+GPT-5.5
+K2.6</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>腾讯研究院AI速递 20260512
-AI能力呈"超指数级"增长，Mythos表现已超过2027年AGI预测线，从2021年8秒任务到2026年16小时任务，每代跃升幅度更大、间隔更短；伟大的公司本质是组织发明，竞争的不只是市场或薪酬而是身份认同…</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>一、Claude Mythos突破评测上限，AGI奇点加速逼近；1.METR最新测试显示Claude Mythos在人类需16小时完成的长线任务上达到50%成功率，直接撑爆评测框架上限，16小时以上区间已无足够样本进行准确测量；；2.AI能力呈"超指数级"增长，Mythos表现已超过2027年AGI…</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://www.sohu.com/a/1021256514_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.3.1778644257183mMjRSDr_324</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>腾讯研究院AI速递 20260529</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Music v2
+ESMFold2
+Wall-OSS-0.5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Music v2
+ESMFold2
+Wall-OSS-0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260603</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.8
+Qwen3.7-Plus</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.8
+Qwen3.7-Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260528</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MiMo-V2.5</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MiMo-V2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260602</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nemotron 3 Ultra
+Cosmos 3
+MPA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Nemotron 3 Ultra
+Cosmos 3
+MPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260601</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.8
+Step 3.7 Flash</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.8
+Step 3.7 Flash</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260527</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Grok V9-Medium
+MiniCPM5-1B
+SkyClaw-v1.0
+Keye-VL-2.0-30B-A3B</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Grok V9-Medium
+MiniCPM5-1B
+SkyClaw-v1.0
+Keye-VL-2.0-30B-A3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260526</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GPT-5.6
+BitCPM-CANN
+AlphaProof Nexus</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GPT-5.6
+BitCPM-CANN
+AlphaProof Nexus</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260525</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GLM-5.1高速版
+LongCat-Video-Avatar 1.5</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GLM-5.1高速版
+LongCat-Video-Avatar 1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260522</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Hy-MT2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Hy-MT2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260521</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Gemini Omni
+Gemini Omni Flash
+Gemini 3.5 Flash
+Qwen3.7-Max
+Co-Scientist
+Robin</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Gemini Omni
+Gemini Omni Flash
+Gemini 3.5 Flash
+Qwen3.7-Max
+Co-Scientist
+Robin</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>25</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260520</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Composer 2.5</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Composer 2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>27</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260519</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>无明确新模型</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>29</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260518</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Gemini 3.5
+Hy3-preview</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Gemini 3.5
+Hy3-preview</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>31</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260515</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.7 Fast</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.7 Fast</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
